--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -4723,12 +4723,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342780</t>
+          <t>339928</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BILLY JOSUE </t>
+          <t xml:space="preserve">CRUZ EDUARDO </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVANTES </t>
+          <t xml:space="preserve">PERAZA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>CASTELO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4758,14 +4758,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6676464851</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6672085305</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4773,60 +4769,56 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>29-04-2011</t>
+          <t>14-07-2001</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BILLYJOSUE29042011@HOTMAIL.COM</t>
+          <t>CRUZEDUARDOCASTELO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 18:09:31</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>02-02-2026 08:58:33</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 18:15:39</t>
+          <t>02-02-2026 09:01:36</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>10-02-2026 18:13:30</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4834,36 +4826,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26060522242920003295</t>
+          <t>26060522002100002445</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>342780</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4873,17 +4865,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ EDUARDO </t>
+          <t xml:space="preserve">BILLY JOSUE </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERAZA </t>
+          <t xml:space="preserve">CERVANTES </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CASTELO</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4893,10 +4885,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6672085305</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6676464851</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4904,56 +4900,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14-07-2001</t>
+          <t>29-04-2011</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CRUZEDUARDOCASTELO@GMAIL.COM</t>
+          <t>BILLYJOSUE29042011@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-02-2026 08:58:33</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:09:31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-02-2026 09:01:36</t>
+          <t>10-02-2026 18:15:39</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>10-02-2026 18:13:30</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4961,36 +4961,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26060522002100002445</t>
+          <t>26060522242920003295</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340205</t>
+          <t>340585</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRISILA </t>
+          <t xml:space="preserve">LEONARDO </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t xml:space="preserve">GASPAR </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t xml:space="preserve">ZATARAIN </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5020,28 +5020,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6671448075</t>
+          <t>6679959449</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-07-2005</t>
+          <t>11-05-2011</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PRISILA.SERRANO2005@ICLOUD.COM</t>
+          <t>LEONARDOGASPARZATARAIN07080@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-02-2026 15:20:49</t>
+          <t>03-02-2026 13:58:23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-02-2026 16:37:01</t>
+          <t>03-02-2026 14:00:16</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5077,7 +5077,7 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5088,19 +5088,11 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26060522046050002591</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522040370002563</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>549</t>
@@ -5108,24 +5100,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341352</t>
+          <t>340589</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5135,17 +5127,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VALENTINA GUADALUPE</t>
+          <t xml:space="preserve">PEDRO LUIS </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAMAN </t>
+          <t xml:space="preserve">IBARRA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">VERDUGO </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5155,28 +5147,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6674827664</t>
+          <t>6674594485</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17-01-2010</t>
+          <t>03-03-2009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VALUSK@GMAIL.COM</t>
+          <t>PEDROLUISIBARRAVERDUGO35@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>05-02-2026 15:45:52</t>
+          <t>03-02-2026 14:12:19</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5201,18 +5193,18 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>06-02-2026 18:52:08</t>
+          <t>04-02-2026 15:54:28</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5223,7 +5215,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26060522145800002952</t>
+          <t>26060522078280002700</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5255,12 +5247,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340585</t>
+          <t>340205</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5270,17 +5262,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONARDO </t>
+          <t xml:space="preserve">PRISILA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">GASPAR </t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZATARAIN </t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5290,28 +5282,28 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6679959449</t>
+          <t>6671448075</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11-05-2011</t>
+          <t>15-07-2005</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>LEONARDOGASPARZATARAIN07080@GMAIL.COM</t>
+          <t>PRISILA.SERRANO2005@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>03-02-2026 13:58:23</t>
+          <t>02-02-2026 15:20:49</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5336,7 +5328,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-02-2026 14:00:16</t>
+          <t>03-02-2026 16:37:01</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5347,7 +5339,7 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5358,11 +5350,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26060522040370002563</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26060522046050002591</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>549</t>
@@ -5370,24 +5370,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340589</t>
+          <t>341352</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO LUIS </t>
+          <t>VALENTINA GUADALUPE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBARRA </t>
+          <t xml:space="preserve">VILLAMAN </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERDUGO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5417,28 +5417,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674594485</t>
+          <t>6674827664</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>03-03-2009</t>
+          <t>17-01-2010</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PEDROLUISIBARRAVERDUGO35@GMAIL.COM</t>
+          <t>VALUSK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-02-2026 14:12:19</t>
+          <t>05-02-2026 15:45:52</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5463,18 +5463,18 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>04-02-2026 15:54:28</t>
+          <t>06-02-2026 18:52:08</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26060522078280002700</t>
+          <t>26060522145800002952</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5517,12 +5517,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340450</t>
+          <t>343615</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5532,17 +5532,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t xml:space="preserve">LARA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t xml:space="preserve">CARO </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5552,67 +5552,75 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6671374207</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6679961093</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMAYA </t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>02-10-1999</t>
+          <t>14-03-2004</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MELISSA_KALEB@ICLOUD.COM</t>
+          <t>RAFAELLARAB31434@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 07:30:06</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 20:47:51</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-02-2026 07:18:54</t>
+          <t>13-02-2026 20:51:57</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13-02-2026 20:50:53</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5620,44 +5628,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26060522099570002774</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060522331420003582</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340701</t>
+          <t>340883</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JESUS IGNACIO</t>
+          <t xml:space="preserve">VINISIO </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILES </t>
+          <t xml:space="preserve">AMAYA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CALVO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5687,14 +5687,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6671315379</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6677918355</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5702,60 +5698,52 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>04-06-2000</t>
+          <t>07-09-1967</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JESUSAVILESGARCIA@GMAIL.COM</t>
+          <t>AMAYACALVO777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 17:05:17</t>
+          <t>04-02-2026 07:43:41</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>05-02-2026 19:12:14</t>
+          <t>06-02-2026 07:50:00</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>05-02-2026 19:11:56</t>
-        </is>
-      </c>
+          <t>06-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5763,7 +5751,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26060522117700002871</t>
+          <t>26060522131260002893</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5773,12 +5761,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5795,12 +5783,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343615</t>
+          <t>340450</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5810,17 +5798,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">LARA </t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARO </t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5830,75 +5818,67 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6679961093</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUMAYA </t>
-        </is>
-      </c>
+          <t>6671374207</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14-03-2004</t>
+          <t>02-10-1999</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>RAFAELLARAB31434@GMAIL.COM</t>
+          <t>MELISSA_KALEB@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13-02-2026 20:47:51</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>03-02-2026 07:30:06</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>13-02-2026 20:51:57</t>
+          <t>05-02-2026 07:18:54</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>13-02-2026 20:50:53</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5906,36 +5886,44 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26060522331420003582</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+          <t>26060522099570002774</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342023</t>
+          <t>340701</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5945,17 +5933,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LARITZA ORALIA</t>
+          <t>JESUS IGNACIO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FARRERA</t>
+          <t xml:space="preserve">AVILES </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5965,32 +5953,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6671880958</t>
+          <t>6671315379</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FINCA GUADALUPANA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14-09-1985</t>
+          <t>04-06-2000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LARYC18@HOTMAIL.COM</t>
+          <t>JESUSAVILESGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:38</t>
+          <t>03-02-2026 17:05:17</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6001,7 +5989,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6011,17 +5999,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-02-2026 07:29:44</t>
+          <t>05-02-2026 19:12:14</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>09-02-2026 07:29:07</t>
+          <t>05-02-2026 19:11:56</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6031,7 +6019,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6041,11 +6029,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26060522183380003064</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+          <t>26060522117700002871</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>499</t>
@@ -6196,12 +6192,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>340883</t>
+          <t>342023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6211,17 +6207,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINISIO </t>
+          <t>LARITZA ORALIA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMAYA </t>
+          <t>FARRERA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CALVO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6231,63 +6227,75 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6677918355</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6671880958</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>FINCA GUADALUPANA</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>07-09-1967</t>
+          <t>14-09-1985</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>AMAYACALVO777@GMAIL.COM</t>
+          <t>LARYC18@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-02-2026 07:43:41</t>
+          <t>09-02-2026 07:10:38</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>06-02-2026 07:50:00</t>
+          <t>09-02-2026 07:29:44</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>06-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>09-02-2026 07:29:07</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6295,22 +6303,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26060522131260002893</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060522183380003064</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6327,12 +6327,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>341188</t>
+          <t>340448</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6342,17 +6342,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MIGUEL </t>
+          <t xml:space="preserve">FERNANDO </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6362,14 +6362,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6671828264</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>HUMAYA</t>
-        </is>
-      </c>
+          <t>6672175555</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6377,60 +6373,52 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15-05-1994</t>
+          <t>25-07-1992</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>DOCTOR_MIGUELESPINOZA@GMAI.COM</t>
+          <t>FMEDINA123098@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-02-2026 20:21:41</t>
+          <t>03-02-2026 07:25:35</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:56</t>
+          <t>03-02-2026 07:27:20</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>04-02-2026 20:27:33</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6438,14 +6426,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26060522089700002751</t>
+          <t>26060522032070002534</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6462,12 +6450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>341315</t>
+          <t>341188</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6477,17 +6465,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CINTIA GUADALUPE </t>
+          <t xml:space="preserve">JOSE MIGUEL </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LLANES</t>
+          <t xml:space="preserve">BELTRAN </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6497,32 +6485,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6677803305</t>
+          <t>6671828264</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAYA </t>
+          <t>HUMAYA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-01-2002</t>
+          <t>15-05-1994</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>GUADALUPE.ROSAS1702@GMAIL.COM</t>
+          <t>DOCTOR_MIGUELESPINOZA@GMAI.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>05-02-2026 14:05:55</t>
+          <t>04-02-2026 20:21:41</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6543,17 +6531,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>05-02-2026 14:09:33</t>
+          <t>04-02-2026 20:27:56</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>05-02-2026 14:09:04</t>
+          <t>04-02-2026 20:27:33</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6563,7 +6551,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6573,7 +6561,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26060522106030002800</t>
+          <t>26060522089700002751</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6585,24 +6573,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>340448</t>
+          <t>341315</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6612,17 +6600,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO </t>
+          <t xml:space="preserve">CINTIA GUADALUPE </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>LLANES</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6632,63 +6620,75 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6672175555</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6677803305</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMAYA </t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25-07-1992</t>
+          <t>17-01-2002</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FMEDINA123098@GMAIL.COM</t>
+          <t>GUADALUPE.ROSAS1702@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>03-02-2026 07:25:35</t>
+          <t>05-02-2026 14:05:55</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:20</t>
+          <t>05-02-2026 14:09:33</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>05-02-2026 14:09:04</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6696,36 +6696,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26060522032070002534</t>
+          <t>26060522106030002800</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>341333</t>
+          <t>340978</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6735,17 +6735,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA PAULA </t>
+          <t>RUSSLY DAOMY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6755,14 +6755,10 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6673202930</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>PORTALEGRE</t>
-        </is>
-      </c>
+          <t>6675725403</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6770,60 +6766,56 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09-03-2000</t>
+          <t>09-02-2004</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>LCANAPAU@GMAIL.COM</t>
+          <t>RUSSLYDAOMY18@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>05-02-2026 14:52:29</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>04-02-2026 12:56:01</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>05-02-2026 14:54:43</t>
+          <t>04-02-2026 13:11:15</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>05-02-2026 14:54:01</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6831,19 +6823,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26060522107500002806</t>
+          <t>26060522074330002693</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Israel  Quintero Dominguez</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6855,12 +6847,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>340978</t>
+          <t>341333</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6870,17 +6862,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RUSSLY DAOMY</t>
+          <t xml:space="preserve">ANA PAULA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6890,10 +6882,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6675725403</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6673202930</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PORTALEGRE</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6901,56 +6897,60 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>09-02-2004</t>
+          <t>09-03-2000</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>RUSSLYDAOMY18@ICLOUD.COM</t>
+          <t>LCANAPAU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>04-02-2026 12:56:01</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>05-02-2026 14:52:29</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>04-02-2026 13:11:15</t>
+          <t>05-02-2026 14:54:43</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>05-02-2026 14:54:01</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6958,19 +6958,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26060522074330002693</t>
+          <t>26060522107500002806</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>Israel  Quintero Dominguez</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6982,12 +6982,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>340874</t>
+          <t>344038</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6997,17 +6997,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MYRIAM LETICIA</t>
+          <t>ADRIAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BRACAMONTES</t>
+          <t>GUARDADO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t>BARRAZA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7017,75 +7017,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6672647413</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>SAN LUIS</t>
-        </is>
-      </c>
+          <t>6671897512</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>01-11-1982</t>
+          <t>07-03-2006</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>MYRIAMLBB@GMAIL.COM</t>
+          <t>ADRIANGUARDADOBARRAZA843@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>04-02-2026 07:16:45</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>16-02-2026 12:15:57</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>04-02-2026 07:20:27</t>
+          <t>18-02-2026 15:51:43</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>04-02-2026 07:19:43</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7093,36 +7085,40 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26060522068050002656</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+          <t>26060522464890003949</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>341458</t>
+          <t>344052</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7132,17 +7128,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MARIA ALEJANDRA</t>
+          <t xml:space="preserve">LUIS ANGEL </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t xml:space="preserve">CORREA </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7152,31 +7148,35 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6677805411</t>
+          <t>6673290264</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>09-03-2011</t>
+          <t>30-10-2007</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>FELIX34@GMAIL.COM</t>
+          <t>LACORREAG12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05-02-2026 20:43:50</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>16-02-2026 12:39:57</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7184,22 +7184,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>12-02-2026 21:02:58</t>
+          <t>16-02-2026 12:41:21</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>12-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -7216,44 +7216,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26060522306770003509</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522387450003675</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Quintero Dominguez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344038</t>
+          <t>344235</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7263,17 +7255,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
+          <t>ANAIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GUARDADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BARRAZA</t>
+          <t>OBESO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7283,67 +7275,79 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6671897512</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6673469159</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SANTA AGRIPINA</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>07-03-2006</t>
+          <t>06-12-1985</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ADRIANGUARDADOBARRAZA843@GMAIL.COM</t>
+          <t>ANAISLO@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 12:15:57</t>
+          <t>16-02-2026 17:45:19</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 15:51:43</t>
+          <t>16-02-2026 17:47:43</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:47:11</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7351,40 +7355,36 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26060522464890003949</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26060522401000003742</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344052</t>
+          <t>340874</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7394,17 +7394,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ANGEL </t>
+          <t>MYRIAM LETICIA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORREA </t>
+          <t>BRACAMONTES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7414,67 +7414,75 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6673290264</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6672647413</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30-10-2007</t>
+          <t>01-11-1982</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>LACORREAG12@GMAIL.COM</t>
+          <t>MYRIAMLBB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 12:39:57</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>04-02-2026 07:16:45</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-02-2026 12:41:21</t>
+          <t>04-02-2026 07:20:27</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>04-02-2026 07:19:43</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7482,19 +7490,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26060522387450003675</t>
+          <t>26060522068050002656</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Israel  Quintero Dominguez</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7506,12 +7514,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344235</t>
+          <t>341458</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7521,17 +7529,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ANAIS</t>
+          <t>MARIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OBESO</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7541,14 +7549,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6673469159</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>SANTA AGRIPINA</t>
-        </is>
-      </c>
+          <t>6677805411</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7556,64 +7560,52 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>06-12-1985</t>
+          <t>09-03-2011</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ANAISLO@OUTLOOK.ES</t>
+          <t>FELIX34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>16-02-2026 17:45:19</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>05-02-2026 20:43:50</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>16-02-2026 17:47:43</t>
+          <t>12-02-2026 21:02:58</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:47:11</t>
-        </is>
-      </c>
+          <t>12-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7621,24 +7613,32 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26060522401000003742</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
+          <t>26060522306770003509</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>341330</t>
+          <t>341911</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7795,17 +7795,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ANGEL </t>
+          <t xml:space="preserve">AMANDA ESTHELA </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MUY</t>
+          <t xml:space="preserve">LAVANDERA </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7815,75 +7815,67 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6673311341</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUMAYA </t>
-        </is>
-      </c>
+          <t>6691588340</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>08-11-1999</t>
+          <t>11-12-1992</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>MUYANGEL08@GMAIL.COM</t>
+          <t>AMADALAVANDERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>05-02-2026 14:46:46</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>08-02-2026 11:13:53</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>05-02-2026 14:50:45</t>
+          <t>08-02-2026 11:16:00</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>05-02-2026 14:49:55</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7891,36 +7883,36 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26060522107430002805</t>
+          <t>26060522170370003014</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342047</t>
+          <t>341330</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7930,17 +7922,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t xml:space="preserve">LUIS ANGEL </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMEZ </t>
+          <t>MUY</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7950,32 +7942,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6672155258</t>
+          <t>6673311341</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIN NOMBRE </t>
+          <t xml:space="preserve">HUMAYA </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19-02-1989</t>
+          <t>08-11-1999</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>VERONICA_AMERICA21@HOTMAIL.COM</t>
+          <t>MUYANGEL08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 08:17:23</t>
+          <t>05-02-2026 14:46:46</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7986,7 +7978,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -7996,17 +7988,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10-02-2026 08:37:13</t>
+          <t>05-02-2026 14:50:45</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>10-02-2026 08:36:47</t>
+          <t>05-02-2026 14:49:55</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8026,19 +8018,11 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26060522225880003233</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>26060522107430002805</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
           <t>499</t>
@@ -8058,12 +8042,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342071</t>
+          <t>342047</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8073,17 +8057,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELANY </t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATIZ </t>
+          <t xml:space="preserve">GAMEZ </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8093,12 +8077,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6674657354</t>
+          <t>6672155258</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SIN NOMBRE</t>
+          <t xml:space="preserve">SIN NOMBRE </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8108,17 +8092,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26-12-2007</t>
+          <t>19-02-1989</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>MELYBATIZALCALA@GMAIL.COM</t>
+          <t>VERONICA_AMERICA21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>09-02-2026 09:28:05</t>
+          <t>09-02-2026 08:17:23</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8139,17 +8123,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>11-02-2026 08:41:28</t>
+          <t>10-02-2026 08:37:13</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>11-02-2026 08:40:53</t>
+          <t>10-02-2026 08:36:47</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8159,7 +8143,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8169,7 +8153,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26060522259830003345</t>
+          <t>26060522225880003233</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -8179,7 +8163,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8201,12 +8185,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>341911</t>
+          <t>342071</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8216,17 +8200,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMANDA ESTHELA </t>
+          <t xml:space="preserve">MELANY </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAVANDERA </t>
+          <t xml:space="preserve">BATIZ </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OLGUIN</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8236,10 +8220,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6691588340</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6674657354</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SIN NOMBRE</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8247,56 +8235,60 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>11-12-1992</t>
+          <t>26-12-2007</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>AMADALAVANDERA@HOTMAIL.COM</t>
+          <t>MELYBATIZALCALA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>08-02-2026 11:13:53</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>09-02-2026 09:28:05</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>08-02-2026 11:16:00</t>
+          <t>11-02-2026 08:41:28</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:40:53</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8304,24 +8296,32 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26060522170370003014</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26060522259830003345</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>342262</t>
+          <t>342265</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8482,17 +8482,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ALEXA KARELYN</t>
+          <t xml:space="preserve">ISABEL </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">ARMIENTA </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6673540771</t>
+          <t>6961096340</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ALCA DEL REY</t>
+          <t xml:space="preserve">ALCALA DEL REY </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8517,17 +8517,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18-04-2007</t>
+          <t>03-03-1999</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ALEXXAK48@GMAIL.COM</t>
+          <t>ISABELARMIENTA02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>09-02-2026 16:35:51</t>
+          <t>09-02-2026 16:38:33</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>11-02-2026 15:34:54</t>
+          <t>11-02-2026 15:36:09</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>11-02-2026 15:34:20</t>
+          <t>11-02-2026 15:35:43</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26060522266750003361</t>
+          <t>26060522266790003362</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8610,12 +8610,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>342445</t>
+          <t>342262</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8625,17 +8625,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER </t>
+          <t>ALEXA KARELYN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">URIARTE </t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">URIARTE </t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6672332266</t>
+          <t>6673540771</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>ALCA DEL REY</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8660,17 +8660,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>23-02-1997</t>
+          <t>18-04-2007</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>JAVIER_EVR@HOTMAIL.COM</t>
+          <t>ALEXXAK48@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>09-02-2026 19:37:37</t>
+          <t>09-02-2026 16:35:51</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>11-02-2026 19:35:21</t>
+          <t>11-02-2026 15:34:54</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11-02-2026 19:34:46</t>
+          <t>11-02-2026 15:34:20</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26060522276930003405</t>
+          <t>26060522266750003361</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8753,12 +8753,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342265</t>
+          <t>342445</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABEL </t>
+          <t xml:space="preserve">JAVIER </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARMIENTA </t>
+          <t xml:space="preserve">URIARTE </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">URIARTE </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6961096340</t>
+          <t>6672332266</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALCALA DEL REY </t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>03-03-1999</t>
+          <t>23-02-1997</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ISABELARMIENTA02@GMAIL.COM</t>
+          <t>JAVIER_EVR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>09-02-2026 16:38:33</t>
+          <t>09-02-2026 19:37:37</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>11-02-2026 15:36:09</t>
+          <t>11-02-2026 19:35:21</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>11-02-2026 15:35:43</t>
+          <t>11-02-2026 19:34:46</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26060522266790003362</t>
+          <t>26060522276930003405</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+          <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8896,12 +8896,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342449</t>
+          <t>342450</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BRAYAN</t>
+          <t xml:space="preserve">LUIS ANGEL </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIGUERA </t>
+          <t xml:space="preserve">PEÑUELAS </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PARTIDA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8931,63 +8931,75 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6671804550</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6671792343</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA CONQUISTA </t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>28-04-2003</t>
+          <t>03-09-2002</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ELREPE0509@ICLOUD.COM</t>
+          <t>PEÑUELASPARTIDALUISANGEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>09-02-2026 19:41:22</t>
+          <t>09-02-2026 19:42:25</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>11-02-2026 19:21:36</t>
+          <t>11-02-2026 19:37:50</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>11-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>11-02-2026 19:37:34</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8995,7 +9007,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26060522276600003404</t>
+          <t>26060522277070003406</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -9005,34 +9017,34 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+          <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Jesus Gilberto Ramos Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>342450</t>
+          <t>342449</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>20266</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9042,17 +9054,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ANGEL </t>
+          <t>BRAYAN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑUELAS </t>
+          <t xml:space="preserve">HIGUERA </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PARTIDA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9062,75 +9074,63 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6671792343</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA CONQUISTA </t>
-        </is>
-      </c>
+          <t>6671804550</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>03-09-2002</t>
+          <t>28-04-2003</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>PEÑUELASPARTIDALUISANGEL@GMAIL.COM</t>
+          <t>ELREPE0509@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>09-02-2026 19:42:25</t>
+          <t>09-02-2026 19:41:22</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>11-02-2026 19:37:50</t>
+          <t>11-02-2026 19:21:36</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>11-02-2026 19:37:34</t>
-        </is>
-      </c>
+          <t>11-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26060522277070003406</t>
+          <t>26060522276600003404</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -9148,34 +9148,34 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Gilberto Ramos Quintero</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345382</t>
+          <t>342789</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87547</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9185,17 +9185,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR FERNANDO </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATUS </t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6331032206</t>
+          <t>6671363151</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAYA </t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9220,24 +9220,20 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>06-11-1987</t>
+          <t>29-05-2001</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CORTESMATUS@HOTMAIL.COM</t>
+          <t>MIGUELFELIX696@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:09:23</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:17:03</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9245,7 +9241,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -9255,17 +9251,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:12:51</t>
+          <t>10-02-2026 18:19:36</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:12:19</t>
+          <t>10-02-2026 18:18:59</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9275,7 +9271,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9285,7 +9281,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26060522533630004162</t>
+          <t>26060522243140003298</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9297,24 +9293,24 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>342696</t>
+          <t>345382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>87547</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9324,17 +9320,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO ANTONIO </t>
+          <t xml:space="preserve">OSCAR FERNANDO </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CORTES</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">MATUS </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9344,12 +9340,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6673278942</t>
+          <t>6331032206</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AGUSTINA RAMIREZ</t>
+          <t xml:space="preserve">HUMAYA </t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9359,17 +9355,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>22-07-2012</t>
+          <t>06-11-1987</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>SILVABELTRAN22@GMAIL.COM</t>
+          <t>CORTESMATUS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>10-02-2026 16:11:20</t>
+          <t>20-02-2026 18:09:23</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9394,17 +9390,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 15:34:52</t>
+          <t>20-02-2026 18:12:51</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>17-02-2026 15:34:04</t>
+          <t>20-02-2026 18:12:19</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9424,19 +9420,11 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26060522431710003849</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522533630004162</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
           <t>499</t>
@@ -9456,12 +9444,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>343134</t>
+          <t>342696</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9471,17 +9459,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DARINA</t>
+          <t xml:space="preserve">PEDRO ANTONIO </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9491,67 +9479,79 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6678757919</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>6673278942</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>AGUSTINA RAMIREZ</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>10-03-2003</t>
+          <t>22-07-2012</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>DARINADUARTE259@GMAIL.COM</t>
+          <t>SILVABELTRAN22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>11-02-2026 20:32:12</t>
+          <t>10-02-2026 16:11:20</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>19-02-2026 08:12:42</t>
+          <t>17-02-2026 15:34:52</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>17-02-2026 15:34:04</t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9559,18 +9559,22 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26060522488960004026</t>
+          <t>26060522431710003849</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9587,12 +9591,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>342789</t>
+          <t>343134</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9602,17 +9606,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>DARINA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9622,75 +9626,67 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6671363151</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6678757919</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>29-05-2001</t>
+          <t>10-03-2003</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>MIGUELFELIX696@GMAIL.COM</t>
+          <t>DARINADUARTE259@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>10-02-2026 18:17:03</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>11-02-2026 20:32:12</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10-02-2026 18:19:36</t>
+          <t>19-02-2026 08:12:42</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>10-02-2026 18:18:59</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9698,36 +9694,40 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26060522243140003298</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
+          <t>26060522488960004026</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>343410</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9737,17 +9737,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA </t>
+          <t xml:space="preserve">IRIS NAYELI </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9757,14 +9757,10 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6672332671</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>PISTACHE</t>
-        </is>
-      </c>
+          <t>6671631520</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9772,17 +9768,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>03-03-1975</t>
+          <t>17-10-2007</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CONTRERAS75@HOTMAIL.COM</t>
+          <t>IRISGARCIACAMACHO02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>13-02-2026 05:35:54</t>
+          <t>15-02-2026 13:04:05</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9792,44 +9788,36 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>18-02-2026 05:37:39</t>
+          <t>15-02-2026 13:05:48</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>18-02-2026 05:36:54</t>
-        </is>
-      </c>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9837,22 +9825,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26060522449660003908</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060522366270003622</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9869,12 +9849,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343846</t>
+          <t>343410</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9884,17 +9864,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRIS NAYELI </t>
+          <t xml:space="preserve">GABRIELA </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9904,10 +9884,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6671631520</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>6672332671</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PISTACHE</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9915,17 +9899,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17-10-2007</t>
+          <t>03-03-1975</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>IRISGARCIACAMACHO02@GMAIL.COM</t>
+          <t>CONTRERAS75@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>15-02-2026 13:04:05</t>
+          <t>13-02-2026 05:35:54</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9935,36 +9919,44 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>15-02-2026 13:05:48</t>
+          <t>18-02-2026 05:37:39</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>18-02-2026 05:36:54</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9972,14 +9964,22 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26060522366270003622</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
+          <t>26060522449660003908</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -9996,12 +9996,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>344320</t>
+          <t>344003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10011,17 +10011,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">LENNIN </t>
+          <t xml:space="preserve">YAJAIRA </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>ARREDONDO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10031,31 +10031,35 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6672021483</t>
+          <t>6674530066</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16-12-2004</t>
+          <t>07-01-1994</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>234567.EXEL@GMAIL.COM</t>
+          <t>YAYIIITAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>16-02-2026 18:55:55</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>16-02-2026 10:33:03</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10063,22 +10067,22 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>16-02-2026 18:58:36</t>
+          <t>16-02-2026 10:34:41</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -10095,36 +10099,36 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26060522406480003778</t>
+          <t>26060522384090003664</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344003</t>
+          <t>344039</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10134,17 +10138,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAJAIRA </t>
+          <t>OLIVER ORLANDO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RABAGO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ARREDONDO</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10154,28 +10158,28 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6674530066</t>
+          <t>6677951630</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>07-01-1994</t>
+          <t>01-03-2007</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>YAYIIITAA@GMAIL.COM</t>
+          <t>OLIVERRABAGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16-02-2026 10:33:03</t>
+          <t>16-02-2026 12:16:04</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10190,28 +10194,28 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>16-02-2026 10:34:41</t>
+          <t>18-02-2026 15:49:33</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V73" t="inlineStr"/>
@@ -10222,36 +10226,40 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26060522384090003664</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
+          <t>26060522464800003948</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344039</t>
+          <t>344156</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10261,17 +10269,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OLIVER ORLANDO</t>
+          <t xml:space="preserve">SAULO ABSALON </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RABAGO</t>
+          <t>RESENDEZ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10281,10 +10289,14 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6677951630</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>6672241298</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>HUMAYA</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10292,56 +10304,64 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01-03-2007</t>
+          <t>16-07-1996</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>OLIVERRABAGO@GMAIL.COM</t>
+          <t>SRESENDE79607@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>16-02-2026 12:16:04</t>
+          <t>16-02-2026 16:19:23</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>18-02-2026 15:49:33</t>
+          <t>16-02-2026 16:33:57</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>16-02-2026 16:33:05</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10349,18 +10369,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26060522464800003948</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26060522395800003710</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10377,12 +10393,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344156</t>
+          <t>344247</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10392,12 +10408,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAULO ABSALON </t>
+          <t xml:space="preserve">JESUS BRAULIO </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RESENDEZ</t>
+          <t xml:space="preserve">CORONEL </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10412,12 +10428,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6672241298</t>
+          <t>6677304788</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>HUMAYA</t>
+          <t xml:space="preserve">HUMAYA </t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10427,42 +10443,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>16-07-1996</t>
+          <t>26-08-1997</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>SRESENDE79607@GMAIL.COM</t>
+          <t>JB.C2QHOMA12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>16-02-2026 16:19:23</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>16-02-2026 18:00:09</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>16-02-2026 16:33:57</t>
+          <t>16-02-2026 18:05:40</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10472,7 +10484,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>16-02-2026 16:33:05</t>
+          <t>16-02-2026 18:04:43</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10492,14 +10504,14 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26060522395800003710</t>
+          <t>26060522402660003752</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10516,12 +10528,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344247</t>
+          <t>344315</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10531,17 +10543,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS BRAULIO </t>
+          <t xml:space="preserve">SERGIO MISAEL </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORONEL </t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">ONTIVEROS </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10551,12 +10563,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6677304788</t>
+          <t>6671429274</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAYA </t>
+          <t xml:space="preserve">CANTABRIA </t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10566,38 +10578,42 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>26-08-1997</t>
+          <t>30-11-1986</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>JB.C2QHOMA12@GMAIL.COM</t>
+          <t>MISAELLI200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:00:09</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>16-02-2026 18:52:30</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:05:40</t>
+          <t>16-02-2026 18:54:24</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10607,7 +10623,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:04:43</t>
+          <t>16-02-2026 18:54:02</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10627,14 +10643,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26060522402660003752</t>
+          <t>26060522406100003771</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10651,12 +10667,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344315</t>
+          <t>344320</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10666,17 +10682,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO MISAEL </t>
+          <t xml:space="preserve">LENNIN </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONTIVEROS </t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10686,14 +10702,10 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6671429274</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CANTABRIA </t>
-        </is>
-      </c>
+          <t>6672021483</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10701,64 +10713,52 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>30-11-1986</t>
+          <t>16-12-2004</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>MISAELLI200@GMAIL.COM</t>
+          <t>234567.EXEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>16-02-2026 18:52:30</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>16-02-2026 18:55:55</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>16-02-2026 18:54:24</t>
+          <t>16-02-2026 18:58:36</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:54:02</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10766,14 +10766,14 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26060522406100003771</t>
+          <t>26060522406480003778</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -10790,12 +10790,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>344223</t>
+          <t>344744</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMILIANO </t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t xml:space="preserve">SARMIENTO </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>QUIROZ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10825,79 +10825,67 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6671178337</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>SANTA AGRIPINA</t>
-        </is>
-      </c>
+          <t>6672327968</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>19-02-2014</t>
+          <t>05-10-1982</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>LIC_JOANRA@HOTMAIL.COM</t>
+          <t>SARMIENTO.DANIEL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>16-02-2026 17:38:41</t>
+          <t>18-02-2026 07:08:56</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:46</t>
+          <t>18-02-2026 07:10:24</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:42:09</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10905,14 +10893,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26060522400500003738</t>
+          <t>26060522456010003914</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10929,12 +10917,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344248</t>
+          <t>344223</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10944,12 +10932,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MARTIN </t>
+          <t xml:space="preserve">EMILIANO </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10959,84 +10947,84 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6671178337</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>SANTA AGRIPINA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>19-02-2014</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>LIC_JOANRA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:38:41</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:42:46</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:42:09</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>7148784113</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>DE LOS NARRADORES 1496</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>16-06-2000</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>NESHUDO13@HOTMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:00:34</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:09:57</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:09:38</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W79" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11044,7 +11032,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26060522403070003753</t>
+          <t>26060522400500003738</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
@@ -11068,12 +11056,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>344744</t>
+          <t>344248</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11083,87 +11071,99 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL </t>
+          <t xml:space="preserve">JESUS MARTIN </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARMIENTO </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>QUIROZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6672327968</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>7148784113</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>DE LOS NARRADORES 1496</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>05-10-1982</t>
+          <t>16-06-2000</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>SARMIENTO.DANIEL@HOTMAIL.COM</t>
+          <t>NESHUDO13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18-02-2026 07:08:56</t>
+          <t>16-02-2026 18:00:34</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>18-02-2026 07:10:24</t>
+          <t>16-02-2026 18:09:57</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:09:38</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11171,14 +11171,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26060522456010003914</t>
+          <t>26060522403070003753</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11195,12 +11195,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>344144</t>
+          <t>345645</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>87810</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11210,17 +11210,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA MARISOL </t>
+          <t>KITZIA AGLAEL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRANDA </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -11230,10 +11230,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>6981085816</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>6674861760</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>REP. DE GUATEMALA</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -11241,17 +11245,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>09-06-2006</t>
+          <t>26-02-1980</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>DANIAMIRANDA612@GMAIL.COM</t>
+          <t>KALEPSA_COMEDORES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>16-02-2026 16:05:40</t>
+          <t>23-02-2026 05:46:16</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11261,36 +11265,44 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>16-02-2026 16:07:55</t>
+          <t>23-02-2026 06:50:53</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr"/>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>23-02-2026 06:50:18</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W81" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11298,36 +11310,44 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>26060522394470003703</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
+          <t>26060522571840004251</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>345936</t>
+          <t>345865</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>88101</t>
+          <t>88030</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11337,17 +11357,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODALIS JAZIBE </t>
+          <t xml:space="preserve">THAMARA GISELA </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t xml:space="preserve">BELTRAN </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELO </t>
+          <t xml:space="preserve">GAMBOA </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11357,10 +11377,14 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6677900975</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>6673047229</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>LIBERTAD</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -11368,56 +11392,64 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>27-11-1998</t>
+          <t>20-01-1996</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>ODALISCASTELO98@GMAIL.COM</t>
+          <t>THAMARABELTRAN38@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>23-02-2026 17:42:08</t>
+          <t>23-02-2026 16:21:25</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>23-02-2026 17:43:19</t>
+          <t>25-02-2026 15:09:39</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:08:54</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11425,14 +11457,22 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26060522592080004350</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
+          <t>26060522654830004544</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -11449,12 +11489,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>345645</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>87810</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11464,17 +11504,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KITZIA AGLAEL</t>
+          <t xml:space="preserve">DANIA MARISOL </t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">MIRANDA </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11484,14 +11524,10 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6674861760</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>REP. DE GUATEMALA</t>
-        </is>
-      </c>
+          <t>6981085816</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -11499,17 +11535,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>26-02-1980</t>
+          <t>09-06-2006</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>KALEPSA_COMEDORES@HOTMAIL.COM</t>
+          <t>DANIAMIRANDA612@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>23-02-2026 05:46:16</t>
+          <t>16-02-2026 16:05:40</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11519,44 +11555,36 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>23-02-2026 06:50:53</t>
+          <t>16-02-2026 16:07:55</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>23-02-2026 06:50:18</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11564,44 +11592,36 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26060522571840004251</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>26060522394470003703</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>345865</t>
+          <t>346260</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>88030</t>
+          <t>88425</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11611,17 +11631,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">THAMARA GISELA </t>
+          <t xml:space="preserve">JOSE ARTURO </t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMBOA </t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11631,79 +11651,67 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6673047229</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>LIBERTAD</t>
-        </is>
-      </c>
+          <t>6677302875</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>20-01-1996</t>
+          <t>19-03-1976</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>THAMARABELTRAN38@GMAIL.COM</t>
+          <t>ARTURO.GAST19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>23-02-2026 16:21:25</t>
+          <t>24-02-2026 17:33:39</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>25-02-2026 15:09:39</t>
+          <t>27-02-2026 17:29:36</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>25-02-2026 15:08:54</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11711,7 +11719,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26060522654830004544</t>
+          <t>26060522720720004766</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -11721,34 +11729,34 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>346216</t>
+          <t>345750</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>88381</t>
+          <t>87915</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11758,17 +11766,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DANNA GUADALUPE</t>
+          <t xml:space="preserve">JESUS FRANCISCO </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>URREA</t>
+          <t>BAEZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11778,63 +11786,79 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6673070869</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>6871911558</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ANTONIO TOPETE 3120</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>09-12-2010</t>
+          <t>10-06-2003</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>LINDURATWICE@GMAIL.COM</t>
+          <t>JFCOHERRERAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>24-02-2026 16:33:41</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>23-02-2026 12:51:04</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>24-02-2026 16:34:55</t>
+          <t>23-02-2026 12:58:58</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:58:24</t>
+        </is>
+      </c>
       <c r="U85" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11842,14 +11866,14 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26060522624910004451</t>
+          <t>26060522579860004289</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11866,12 +11890,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>345750</t>
+          <t>345936</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>87915</t>
+          <t>88101</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11881,17 +11905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS FRANCISCO </t>
+          <t xml:space="preserve">ODALIS JAZIBE </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t xml:space="preserve">CASTELO </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -11901,32 +11925,28 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6871911558</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>ANTONIO TOPETE 3120</t>
-        </is>
-      </c>
+          <t>6677900975</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>10-06-2003</t>
+          <t>27-11-1998</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>JFCOHERRERAB@GMAIL.COM</t>
+          <t>ODALISCASTELO98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>23-02-2026 12:51:04</t>
+          <t>23-02-2026 17:42:08</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -11936,22 +11956,22 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>23-02-2026 12:58:58</t>
+          <t>23-02-2026 17:43:19</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -11959,21 +11979,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>23-02-2026 12:58:24</t>
-        </is>
-      </c>
+      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11981,14 +11993,14 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>26060522579860004289</t>
+          <t>26060522592080004350</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
@@ -12005,12 +12017,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>346260</t>
+          <t>345939</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>88425</t>
+          <t>88104</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12020,17 +12032,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ARTURO </t>
+          <t xml:space="preserve">ABIGAIL </t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">GASTELUM </t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -12040,33 +12052,33 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6677302875</t>
+          <t>6673173173</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>19-03-1976</t>
+          <t>21-09-1999</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ARTURO.GAST19@GMAIL.COM</t>
+          <t>ABIGAILMEDZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>24-02-2026 17:33:39</t>
+          <t>23-02-2026 17:45:24</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -12076,22 +12088,22 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>27-02-2026 17:29:36</t>
+          <t>23-02-2026 17:46:45</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -12108,44 +12120,36 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26060522720720004766</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>26060522592380004353</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>347060</t>
+          <t>346216</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>89225</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12155,17 +12159,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MIGUEL </t>
+          <t>DANNA GUADALUPE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>URREA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12175,79 +12179,63 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6673544549</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUMAYA </t>
-        </is>
-      </c>
+          <t>6673070869</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>04-04-2003</t>
+          <t>09-12-2010</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>YONAQUO@GMAIL.COM</t>
+          <t>LINDURATWICE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>27-02-2026 19:08:50</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 16:33:41</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>27-02-2026 19:12:20</t>
+          <t>24-02-2026 16:34:55</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>27-02-2026 19:11:49</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12255,14 +12243,14 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26060522724320004781</t>
+          <t>26060522624910004451</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -12279,12 +12267,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>345939</t>
+          <t>347060</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>88104</t>
+          <t>89225</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12294,17 +12282,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABIGAIL </t>
+          <t xml:space="preserve">JOSE MIGUEL </t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t xml:space="preserve">ROJO </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -12314,67 +12302,79 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6673173173</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>6673544549</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMAYA </t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>21-09-1999</t>
+          <t>04-04-2003</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>ABIGAILMEDZ@GMAIL.COM</t>
+          <t>YONAQUO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>23-02-2026 17:45:24</t>
+          <t>27-02-2026 19:08:50</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>23-02-2026 17:46:45</t>
+          <t>27-02-2026 19:12:20</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>27-02-2026 19:11:49</t>
+        </is>
+      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W89" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12382,14 +12382,14 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>26060522592380004353</t>
+          <t>26060522724320004781</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>347645</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>89810</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t xml:space="preserve">CARRILLO </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,47 +895,43 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671179688</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UIVERSIDAD</t>
-        </is>
-      </c>
+          <t>6673600123</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>03-06-1995</t>
+          <t>20-08-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+          <t>EDUCARRILLO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:01:52</t>
+          <t>02-03-2026 15:48:42</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -945,29 +941,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:55</t>
+          <t>03-03-2026 15:19:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:06:38</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -975,11 +963,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26060522800030004926</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26060522843550005067</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -1120,6 +1116,280 @@
       <c r="AC5" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>348005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90170</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CALI ANAHI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUIÑONEZ </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6674282879</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>19-09-2001</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CALILEON_01@HOTMIAL.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:00:50</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:04:01</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>26060522837030005043</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>347656</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>89821</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUARDO </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6671179688</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UIVERSIDAD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>03-06-1995</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:01:52</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:55</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:38</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26060522800030004926</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,12 +995,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347755</t>
+          <t>347656</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>89821</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,10 +1030,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6674593000</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6671179688</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UIVERSIDAD</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1041,32 +1045,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>09-04-2011</t>
+          <t>03-06-1995</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>94211SANTYGONRU@GMAIL.COM</t>
+          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:27</t>
+          <t>02-03-2026 16:01:52</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1076,7 +1080,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:15</t>
+          <t>02-03-2026 16:06:55</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1084,13 +1088,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:38</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1098,7 +1110,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26060522807360004966</t>
+          <t>26060522800030004926</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1110,12 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>347755</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,14 +1304,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6671179688</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>UIVERSIDAD</t>
-        </is>
-      </c>
+          <t>6674593000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1307,32 +1315,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-06-1995</t>
+          <t>09-04-2011</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+          <t>94211SANTYGONRU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:01:52</t>
+          <t>02-03-2026 17:37:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1342,7 +1350,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:55</t>
+          <t>02-03-2026 17:39:15</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1350,21 +1358,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:06:38</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26060522800030004926</t>
+          <t>26060522807360004966</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1384,10 +1384,272 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>348752</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90917</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NATHALY DENISSE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMOS </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BRUNN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6671897221</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>28-02-1997</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:41:25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:31</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:43:52</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26060522921900005358</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Jesus Gilberto Ramos Quintero</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348670</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90835</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA CRISTINA </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OBESO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6671262646</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23-05-1977</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>KEYCHA7@YHOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:53:30</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:55:38</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26060522914020005327</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346569</t>
+          <t>345998</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88734</t>
+          <t>88163</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMILY </t>
+          <t>DIANA LAURA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJOS </t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t xml:space="preserve">VERDUGO </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6671768750</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6734723540</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMAYA </t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,56 +628,64 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-02-2008</t>
+          <t>20-01-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ALEJOSEMILY3@GMAIL.COM</t>
+          <t>DIANALCV98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25-02-2026 18:23:46</t>
+          <t>23-02-2026 18:41:26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:18:16</t>
+          <t>02-03-2026 19:21:26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:20:33</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26060522811240004986</t>
+          <t>26060522816200005001</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -696,7 +708,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -713,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>345998</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88163</t>
+          <t>88734</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIANA LAURA</t>
+          <t xml:space="preserve">EMILY </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">ALEJOS </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERDUGO </t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,14 +760,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6734723540</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUMAYA </t>
-        </is>
-      </c>
+          <t>6671768750</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -763,64 +771,56 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-01-1998</t>
+          <t>22-02-2008</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DIANALCV98@GMAIL.COM</t>
+          <t>ALEJOSEMILY3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>23-02-2026 18:41:26</t>
+          <t>25-02-2026 18:23:46</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 19:21:26</t>
+          <t>02-03-2026 18:18:16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:20:33</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26060522816200005001</t>
+          <t>26060522811240004986</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -860,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347645</t>
+          <t>347656</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>89821</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRILLO </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,43 +895,47 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6673600123</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6671179688</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UIVERSIDAD</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-08-2003</t>
+          <t>03-06-1995</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EDUCARRILLO@OUTLOOK.COM</t>
+          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 15:48:42</t>
+          <t>02-03-2026 16:01:52</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -941,21 +945,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 15:19:51</t>
+          <t>02-03-2026 16:06:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:38</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -963,19 +975,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26060522843550005067</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522800030004926</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -995,12 +999,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>348005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>CALI ANAHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t xml:space="preserve">QUIÑONEZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,79 +1034,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6671179688</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>UIVERSIDAD</t>
-        </is>
-      </c>
+          <t>6674282879</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>03-06-1995</t>
+          <t>19-09-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+          <t>CALILEON_01@HOTMIAL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:01:52</t>
+          <t>03-03-2026 11:00:50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:55</t>
+          <t>03-03-2026 11:04:01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:06:38</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1110,14 +1102,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26060522800030004926</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26060522837030005043</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1134,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348005</t>
+          <t>347755</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CALI ANAHI</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUIÑONEZ </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,33 +1169,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6674282879</t>
+          <t>6674593000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19-09-2001</t>
+          <t>09-04-2011</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CALILEON_01@HOTMIAL.COM</t>
+          <t>94211SANTYGONRU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 11:00:50</t>
+          <t>02-03-2026 17:37:27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1205,28 +1205,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 11:04:01</t>
+          <t>02-03-2026 17:39:15</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1237,44 +1237,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26060522837030005043</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060522807360004966</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347755</t>
+          <t>348614</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>90779</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">SALVADOR </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,7 +1296,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6674593000</t>
+          <t>6671260174</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,17 +1307,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09-04-2011</t>
+          <t>23-03-1965</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>94211SANTYGONRU@GMAIL.COM</t>
+          <t>SALVADORBAJO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:27</t>
+          <t>05-03-2026 06:05:05</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1350,12 +1342,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:15</t>
+          <t>07-03-2026 07:21:41</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1372,11 +1364,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26060522807360004966</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26060522969080005509</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348752</t>
+          <t>348670</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>90835</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NATHALY DENISSE</t>
+          <t xml:space="preserve">ANA CRISTINA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRUNN</t>
+          <t>OBESO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,14 +1431,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6671897221</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
+          <t>6671262646</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1446,64 +1442,52 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>23-05-1977</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
+          <t>KEYCHA7@YHOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>05-03-2026 16:41:25</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>05-03-2026 11:53:30</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:31</t>
+          <t>05-03-2026 11:55:38</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:43:52</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1511,36 +1495,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26060522921900005358</t>
+          <t>26060522914020005327</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Jesus Gilberto Ramos Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348670</t>
+          <t>348752</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>90917</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA CRISTINA </t>
+          <t>NATHALY DENISSE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OBESO</t>
+          <t>BRUNN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,10 +1554,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6671262646</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6671897221</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1581,52 +1569,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-05-1977</t>
+          <t>28-02-1997</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>KEYCHA7@YHOTMAIL.COM</t>
+          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>05-03-2026 11:53:30</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>05-03-2026 16:41:25</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 11:55:38</t>
+          <t>05-03-2026 16:44:31</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:43:52</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1634,24 +1634,294 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26060522914020005327</t>
+          <t>26060522921900005358</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>Jesus Gilberto Ramos Quintero</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347645</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89810</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUARDO </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRILLO </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6673600123</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>20-08-2003</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>EDUCARRILLO@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:48:42</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:19:51</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26060522843550005067</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348613</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90778</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA DOLORES </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUJILLO </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TORTOLEDO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6672292890</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>30-09-1972</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>LOLISTRUJILLO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>05-03-2026 06:01:50</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>07-03-2026 07:20:33</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26060522969030005508</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Brayan Ramiro Armienta Perez</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>345998</t>
+          <t>282023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88163</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIANA LAURA</t>
+          <t xml:space="preserve">GITZIA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERDUGO </t>
+          <t xml:space="preserve">RUBIO </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6734723540</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUMAYA </t>
-        </is>
-      </c>
+          <t>6673828519</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -628,64 +624,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-01-1998</t>
+          <t>29-12-1995</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DIANALCV98@GMAIL.COM</t>
+          <t>GITZIARUBIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23-02-2026 18:41:26</t>
+          <t>06-03-2025 17:14:41</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 19:21:26</t>
+          <t>17-03-2026 18:17:12</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:20:33</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26060522816200005001</t>
+          <t>26060523265230006444</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -701,14 +689,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -725,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346569</t>
+          <t>345998</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88734</t>
+          <t>88163</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMILY </t>
+          <t>DIANA LAURA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJOS </t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t xml:space="preserve">VERDUGO </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,10 +744,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671768750</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6734723540</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMAYA </t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -771,42 +759,42 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-02-2008</t>
+          <t>20-01-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ALEJOSEMILY3@GMAIL.COM</t>
+          <t>DIANALCV98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-02-2026 18:23:46</t>
+          <t>23-02-2026 18:41:26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:18:16</t>
+          <t>02-03-2026 19:21:26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -814,13 +802,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:20:33</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,7 +824,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26060522811240004986</t>
+          <t>26060522816200005001</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -843,7 +839,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -860,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>326558</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>MONICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,39 +891,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671179688</t>
+          <t>6671007141</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>UIVERSIDAD</t>
+          <t>POLO SUR</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>03-06-1995</t>
+          <t>19-01-1990</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+          <t>ALEACOSTA.R19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:01:52</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-12-2025 09:18:42</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -935,27 +927,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:55</t>
+          <t>17-03-2026 17:30:10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:38</t>
+          <t>17-03-2026 17:26:30</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,36 +967,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26060522800030004926</t>
+          <t>26060523261690006428</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Gilberto Ramos Quintero</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>348005</t>
+          <t>326712</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CALI ANAHI</t>
+          <t xml:space="preserve">HEMILI </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUIÑONEZ </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>GALLARDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,7 +1026,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6674282879</t>
+          <t>6673555124</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,22 +1037,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19-09-2001</t>
+          <t>22-12-2004</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CALILEON_01@HOTMIAL.COM</t>
+          <t>HEMILIGARCIA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-03-2026 11:00:50</t>
+          <t>04-12-2025 10:41:01</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1070,28 +1062,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 11:04:01</t>
+          <t>19-03-2026 19:51:41</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1102,7 +1094,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26060522837030005043</t>
+          <t>26060523342550006726</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1117,7 +1109,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1134,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347755</t>
+          <t>346570</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>88735</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">ANTONIO RAFAEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">ALEJOS </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">ACUÑA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,7 +1161,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6674593000</t>
+          <t>6671631010</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,17 +1172,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09-04-2011</t>
+          <t>05-01-2010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>94211SANTYGONRU@GMAIL.COM</t>
+          <t>MIVITOTA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:27</t>
+          <t>25-02-2026 18:26:17</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1215,12 +1207,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:15</t>
+          <t>10-03-2026 18:58:43</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1237,11 +1229,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26060522807360004966</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26060523066340005831</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1249,24 +1249,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348614</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90779</t>
+          <t>88734</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALVADOR </t>
+          <t xml:space="preserve">EMILY </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t xml:space="preserve">ALEJOS </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,28 +1296,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6671260174</t>
+          <t>6671768750</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-03-1965</t>
+          <t>22-02-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SALVADORBAJO@OUTLOOK.COM</t>
+          <t>ALEJOSEMILY3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-03-2026 06:05:05</t>
+          <t>25-02-2026 18:23:46</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>07-03-2026 07:21:41</t>
+          <t>02-03-2026 18:18:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26060522969080005509</t>
+          <t>26060522811240004986</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+          <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,24 +1384,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348670</t>
+          <t>347679</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>89844</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA CRISTINA </t>
+          <t xml:space="preserve">OSCAR </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OBESO</t>
+          <t xml:space="preserve">VILLARREAL </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,28 +1431,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6671262646</t>
+          <t>6961078645</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-05-1977</t>
+          <t>21-11-1975</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>KEYCHA7@YHOTMAIL.COM</t>
+          <t>SAN.OSCARBB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>05-03-2026 11:53:30</t>
+          <t>02-03-2026 16:32:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1473,18 +1473,18 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-03-2026 11:55:38</t>
+          <t>18-03-2026 18:33:54</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>17-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1495,10 +1495,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26060522914020005327</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26060523303660006581</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1507,24 +1511,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348752</t>
+          <t>347755</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NATHALY DENISSE</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BRUNN</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,79 +1558,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6671897221</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
+          <t>6674593000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>09-04-2011</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
+          <t>94211SANTYGONRU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>05-03-2026 16:41:25</t>
+          <t>02-03-2026 17:37:27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:31</t>
+          <t>02-03-2026 17:39:15</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:43:52</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1634,19 +1626,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26060522921900005358</t>
+          <t>26060522807360004966</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Jesus Gilberto Ramos Quintero</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1658,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347645</t>
+          <t>347656</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>89821</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1678,12 +1670,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRILLO </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,43 +1685,47 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6673600123</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6671179688</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UIVERSIDAD</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20-08-2003</t>
+          <t>03-06-1995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EDUCARRILLO@OUTLOOK.COM</t>
+          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:48:42</t>
+          <t>02-03-2026 16:01:52</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1739,21 +1735,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 15:19:51</t>
+          <t>02-03-2026 16:06:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:38</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1761,19 +1765,11 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26060522843550005067</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522800030004926</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1793,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348613</t>
+          <t>348005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90778</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DOLORES </t>
+          <t>CALI ANAHI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUJILLO </t>
+          <t xml:space="preserve">QUIÑONEZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TORTOLEDO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,7 +1824,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6672292890</t>
+          <t>6674282879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1839,22 +1835,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-09-1972</t>
+          <t>19-09-2001</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LOLISTRUJILLO@HOTMAIL.COM</t>
+          <t>CALILEON_01@HOTMIAL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-03-2026 06:01:50</t>
+          <t>03-03-2026 11:00:50</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1864,28 +1860,28 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>07-03-2026 07:20:33</t>
+          <t>03-03-2026 11:04:01</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1896,32 +1892,4157 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>26060522837030005043</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347645</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>89810</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUARDO </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRILLO </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6673600123</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>20-08-2003</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>EDUCARRILLO@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:48:42</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:19:51</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26060522843550005067</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348613</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90778</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA DOLORES </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUJILLO </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TORTOLEDO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6672292890</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30-09-1972</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LOLISTRUJILLO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>05-03-2026 06:01:50</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>07-03-2026 07:20:33</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>26060522969030005508</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348729</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90894</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHANA GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOZA </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PALAZUELOS </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6671283394</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>19-11-2003</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>JOHANAESPINOZA2116@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:23:57</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26060523013730005631</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348774</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90939</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE PABLO </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LEYVA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6677806207</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANACO </t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>29-03-2003</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PABLITO03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:48:03</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:04:19</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:03:57</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26060523260380006422</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348752</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90917</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NATHALY DENISSE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMOS </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BRUNN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6671897221</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>28-02-1997</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:41:25</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:31</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:43:52</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26060522921900005358</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Jesus Gilberto Ramos Quintero</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348614</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90779</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALVADOR </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAJO </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6671260174</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>23-03-1965</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SALVADORBAJO@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>05-03-2026 06:05:05</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>07-03-2026 07:21:41</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26060522969080005509</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Brayan Ramiro Armienta Perez</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>349589</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91754</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATRICIA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OVIEDO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORIS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6674109315</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>11-09-1983</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PATTYOV11@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:03:55</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:05:04</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26060523020730005655</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349640</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91805</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KARELI </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEÑA </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6961173944</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>09-12-2004</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>KARELICORRALES9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:59:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:05:01</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26060523025670005681</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349751</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91916</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIBEL </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6672345777</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>25-03-1967</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MARIBEL_67@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10-03-2026 06:53:41</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>10-03-2026 06:55:24</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26060523042870005733</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348670</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90835</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA CRISTINA </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OBESO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6671262646</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>23-05-1977</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>KEYCHA7@YHOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:53:30</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:55:38</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26060522914020005327</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349576</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91741</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GILBERTO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRAGAN </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6672221440</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ALCAPARRA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>22-11-1994</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>GIL.ALBERSO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:57:46</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:01:05</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:00:11</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26060523020360005653</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349625</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91790</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RAMON ESAU</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUBIO </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6676937404</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>20-08-1993</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ESAURUBIO5831@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:47:46</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:50:49</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26060523024360005676</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>349774</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91939</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEDANO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6671016755</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>07-09-1990</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>GUTIERREZRAGS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:45:11</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:47:28</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>09-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26060523045860005747</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>349991</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>92156</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALAN </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6676925232</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DORADO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>15-09-2002</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ALANMEZAVZLA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:27:13</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:33:17</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:32:45</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26060523068710005843</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>349990</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>92155</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARAHI </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALENZUELA </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6671853221</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>10-04-1999</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>SARAHIMEZVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:25:07</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:33:17</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26060523068710005843</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>350064</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>92229</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS ALONSO </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURO </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6231180361</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10-09-2011</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>LMURO985@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11-03-2026 09:45:44</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:18:56</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26060523121110006024</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>350100</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>92265</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DENIS ADRIANA </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYAN </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESQUIVEL </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6673096295</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ALGARROBO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>09-03-1996</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DENISPAYAN0903@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11-03-2026 13:21:16</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:28:20</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:27:41</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26060523123440006033</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Israel  Quintero Dominguez</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>350877</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>93041</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ARIANNA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GASTELUM</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOTO </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6674503791</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>06-06-2008</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>GASTELUMSOTOARIANA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>15-03-2026 11:28:27</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:42:30</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26060523274250006479</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>350026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92191</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGINA LIZETTE </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6671370524</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C ORDUNA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>14-07-1981</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>GEORGY147@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>11-03-2026 05:11:21</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:02:06</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:01:18</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26060523202360006243</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Brayan Ramiro Armienta Perez</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>350255</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92419</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JUAN PABLO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">URIAS </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6674151957</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C ORDUÑA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>18-12-1977</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>JP_URIAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>12-03-2026 06:08:05</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:04:21</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:03:49</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26060523202410006245</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Brayan Ramiro Armienta Perez</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>351445</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>93609</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEODORO ALONSO </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FRAILE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6673505959</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>DIEGO DE GUZMAN</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>12-08-2000</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>TEO_ALONSO12@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:50:21</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:56:41</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:55:40</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26060523248920006377</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351718</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93882</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ROSA ILIANA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOTO </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MOLINA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6674737628</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>21-05-1977</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ILIANASOTOMOLIMA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:38:02</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:47:52</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26060523274460006480</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>351405</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93569</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOCORRO ISABEL </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERNAL </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VARELAS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5530312690</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C NORTE</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>27-06-1970</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SOCORROISABEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>17-03-2026 06:30:16</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17-03-2026 06:47:36</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17-03-2026 06:46:44</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26060523244000006351</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>351444</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93608</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA JOSE </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ZAVALA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6673511019</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>11-06-2000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>MJLOPEZZAVALA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:45:54</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:56:41</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26060523248920006377</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>350324</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>92488</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EFRAIN </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ARAUJO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ZAZUETA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6671205525</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>25-08-1964</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>COMANDANCIA@BOMBEROSCULIACAN.ORG.MX</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:10:55</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:12:30</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26060523122060006029</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>351368</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>93532</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAYRIN </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUZMAN </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6675431656</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>31-12-2006</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MAYRINJ144@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:14:16</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:16:29</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26060523234800006340</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>351960</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>94124</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELISA NICOLE </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELAZQUEZ </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACOSTA </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6677805160</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>01-08-2010</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ELISANVA10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:47:19</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:51:51</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26060523304800006585</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>351540</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>93704</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OSMAR ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIRADO </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6671063417</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12-03-2012</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OSMARTIRADO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:29:05</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>19-03-2026 15:34:57</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26060523330960006674</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Israel  Quintero Dominguez</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>351940</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>94104</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTIAGO </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE LA CRUZ </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6673408053</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10-03-2012</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>SAN.OSCARB@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:28:20</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:29:39</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26060523303240006578</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>351717</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>93881</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LUIS MANUEL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ENCINES</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6679968685</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22-07-2008</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>LUISMENORT20@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:30:18</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:49:28</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26060523274500006482</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>351952</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>94116</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA LETICIA </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUILAR </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALLEGOS </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6674213362</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES MAGON </t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>16-09-1971</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>JONGAJEOLA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:39:51</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:15:34</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:15:14</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26060523343550006730</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282023</t>
+          <t>211404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79524</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GITZIA </t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6673828519</t>
+          <t>6674574069</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>29-12-1995</t>
+          <t>21-11-2003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>GITZIARUBIO@GMAIL.COM</t>
+          <t>TARRIA08LG@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>06-03-2025 17:14:41</t>
+          <t>26-12-2023 15:57:54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -659,18 +659,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17-03-2026 18:17:12</t>
+          <t>30-03-2026 15:15:52</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>29-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,14 +681,10 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26060523265230006444</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26060523631540007561</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -856,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>326558</t>
+          <t>282023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MONICA ALEJANDRA</t>
+          <t xml:space="preserve">GITZIA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t xml:space="preserve">RUBIO </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,14 +887,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671007141</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>POLO SUR</t>
-        </is>
-      </c>
+          <t>6673828519</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -906,38 +898,42 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19-01-1990</t>
+          <t>29-12-1995</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEACOSTA.R19@GMAIL.COM</t>
+          <t>GITZIARUBIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>03-12-2025 09:18:42</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>06-03-2025 17:14:41</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-03-2026 17:30:10</t>
+          <t>17-03-2026 18:17:12</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -945,21 +941,13 @@
           <t>16-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>17-03-2026 17:26:30</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,36 +955,40 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26060523261690006428</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26060523265230006444</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Jesus Gilberto Ramos Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>326712</t>
+          <t>326558</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEMILI </t>
+          <t>MONICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GALLARDO</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,10 +1018,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6673555124</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6671007141</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>POLO SUR</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1037,56 +1033,60 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22-12-2004</t>
+          <t>19-01-1990</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HEMILIGARCIA22@GMAIL.COM</t>
+          <t>ALEACOSTA.R19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>04-12-2025 10:41:01</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>03-12-2025 09:18:42</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>19-03-2026 19:51:41</t>
+          <t>17-03-2026 17:30:10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:26:30</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,44 +1094,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26060523342550006726</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060523261690006428</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Gilberto Ramos Quintero</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346570</t>
+          <t>326712</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88735</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO RAFAEL </t>
+          <t xml:space="preserve">HEMILI </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJOS </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACUÑA </t>
+          <t>GALLARDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,33 +1153,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6671631010</t>
+          <t>6673555124</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05-01-2010</t>
+          <t>22-12-2004</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MIVITOTA@HOTMAIL.COM</t>
+          <t>HEMILIGARCIA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25-02-2026 18:26:17</t>
+          <t>04-12-2025 10:41:01</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1207,12 +1199,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10-03-2026 18:58:43</t>
+          <t>19-03-2026 19:51:41</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1229,7 +1221,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26060523066340005831</t>
+          <t>26060523342550006726</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1396,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347679</t>
+          <t>346570</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>88735</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR </t>
+          <t xml:space="preserve">ANTONIO RAFAEL </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">ALEJOS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLARREAL </t>
+          <t xml:space="preserve">ACUÑA </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,7 +1423,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6961078645</t>
+          <t>6671631010</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,20 +1434,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-11-1975</t>
+          <t>05-01-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SAN.OSCARBB@GMAIL.COM</t>
+          <t>MIVITOTA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:32:28</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>25-02-2026 18:26:17</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1463,28 +1459,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18-03-2026 18:33:54</t>
+          <t>10-03-2026 18:58:43</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1495,40 +1491,44 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26060523303660006581</t>
+          <t>26060523066340005831</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347755</t>
+          <t>348005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>CALI ANAHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">QUIÑONEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,33 +1558,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6674593000</t>
+          <t>6674282879</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>09-04-2011</t>
+          <t>19-09-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>94211SANTYGONRU@GMAIL.COM</t>
+          <t>CALILEON_01@HOTMIAL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:27</t>
+          <t>03-03-2026 11:00:50</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1594,28 +1594,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:15</t>
+          <t>03-03-2026 11:04:01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1626,36 +1626,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26060522807360004966</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26060522837030005043</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>347755</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,14 +1693,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6671179688</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>UIVERSIDAD</t>
-        </is>
-      </c>
+          <t>6674593000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1700,32 +1704,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-06-1995</t>
+          <t>09-04-2011</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
+          <t>94211SANTYGONRU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:01:52</t>
+          <t>02-03-2026 17:37:27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1735,7 +1739,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:06:55</t>
+          <t>02-03-2026 17:39:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1743,21 +1747,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:06:38</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1765,7 +1761,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26060522800030004926</t>
+          <t>26060522807360004966</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1777,24 +1773,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348005</t>
+          <t>347645</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>89810</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1800,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CALI ANAHI</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUIÑONEZ </t>
+          <t xml:space="preserve">CARRILLO </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,7 +1820,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674282879</t>
+          <t>6673600123</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1835,22 +1831,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19-09-2001</t>
+          <t>20-08-2003</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CALILEON_01@HOTMIAL.COM</t>
+          <t>EDUCARRILLO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 11:00:50</t>
+          <t>02-03-2026 15:48:42</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1860,22 +1856,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 11:04:01</t>
+          <t>03-03-2026 15:19:51</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1892,7 +1888,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26060522837030005043</t>
+          <t>26060522843550005067</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1902,12 +1898,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+          <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1924,12 +1920,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347645</t>
+          <t>347656</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>89821</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1944,12 +1940,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRILLO </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,43 +1955,47 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6673600123</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6671179688</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UIVERSIDAD</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20-08-2003</t>
+          <t>03-06-1995</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EDUCARRILLO@OUTLOOK.COM</t>
+          <t>ALEXISORTIZ0306@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:48:42</t>
+          <t>02-03-2026 16:01:52</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2005,21 +2005,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 15:19:51</t>
+          <t>02-03-2026 16:06:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:06:38</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2027,19 +2035,11 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26060522843550005067</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522800030004926</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2059,12 +2059,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348613</t>
+          <t>349640</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90778</t>
+          <t>91805</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DOLORES </t>
+          <t xml:space="preserve">KARELI </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUJILLO </t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TORTOLEDO</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6672292890</t>
+          <t>6961173944</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30-09-1972</t>
+          <t>09-12-2004</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>LOLISTRUJILLO@HOTMAIL.COM</t>
+          <t>KARELICORRALES9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>05-03-2026 06:01:50</t>
+          <t>09-03-2026 18:59:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-03-2026 07:20:33</t>
+          <t>09-03-2026 19:05:01</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2162,19 +2162,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26060522969030005508</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060523025670005681</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2182,24 +2174,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348729</t>
+          <t>349751</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90894</t>
+          <t>91916</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHANA GUADALUPE </t>
+          <t xml:space="preserve">MARIBEL </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PALAZUELOS </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,7 +2221,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6671283394</t>
+          <t>6672345777</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,20 +2232,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19-11-2003</t>
+          <t>25-03-1967</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JOHANAESPINOZA2116@GMAIL.COM</t>
+          <t>MARIBEL_67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-03-2026 15:36:10</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>10-03-2026 06:53:41</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2261,22 +2257,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>09-03-2026 16:23:57</t>
+          <t>10-03-2026 06:55:24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2293,22 +2289,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26060523013730005631</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060523042870005733</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2325,12 +2313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348774</t>
+          <t>349576</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90939</t>
+          <t>91741</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2328,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE PABLO </t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t xml:space="preserve">BARRAGAN </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,12 +2348,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6677806207</t>
+          <t>6672221440</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANACO </t>
+          <t>ALCAPARRA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2375,52 +2363,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>29-03-2003</t>
+          <t>22-11-1994</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PABLITO03@GMAIL.COM</t>
+          <t>GIL.ALBERSO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>05-03-2026 17:48:03</t>
+          <t>09-03-2026 17:57:46</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>17-03-2026 17:04:19</t>
+          <t>09-03-2026 18:01:05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>17-03-2026 17:03:57</t>
+          <t>09-03-2026 18:00:11</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2440,22 +2428,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26060523260380006422</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060523020360005653</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2472,12 +2452,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348752</t>
+          <t>348613</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2467,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NATHALY DENISSE</t>
+          <t xml:space="preserve">MARIA DOLORES </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">TRUJILLO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BRUNN</t>
+          <t>TORTOLEDO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,14 +2487,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6671897221</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
+          <t>6672292890</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2522,64 +2498,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>30-09-1972</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
+          <t>LOLISTRUJILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-03-2026 16:41:25</t>
+          <t>05-03-2026 06:01:50</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:31</t>
+          <t>07-03-2026 07:20:33</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:43:52</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2587,19 +2555,27 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26060522921900005358</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26060522969030005508</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Gilberto Ramos Quintero</t>
+          <t>Brayan Ramiro Armienta Perez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2611,12 +2587,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348614</t>
+          <t>348729</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90779</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2626,17 +2602,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALVADOR </t>
+          <t xml:space="preserve">JOHANA GUADALUPE </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">PALAZUELOS </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2646,35 +2622,31 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6671260174</t>
+          <t>6671283394</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23-03-1965</t>
+          <t>19-11-2003</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SALVADORBAJO@OUTLOOK.COM</t>
+          <t>JOHANAESPINOZA2116@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-03-2026 06:05:05</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>05-03-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2682,22 +2654,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-03-2026 07:21:41</t>
+          <t>09-03-2026 16:23:57</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>08-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2714,7 +2686,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26060522969080005509</t>
+          <t>26060523013730005631</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2724,34 +2696,34 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+          <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>349589</t>
+          <t>348774</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>90939</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA </t>
+          <t xml:space="preserve">JOSE PABLO </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OVIEDO</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NORIS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,28 +2753,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6674109315</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6677806207</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANACO </t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11-09-1983</t>
+          <t>29-03-2003</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PATTYOV11@HOTMAIL.COM</t>
+          <t>PABLITO03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-03-2026 18:03:55</t>
+          <t>05-03-2026 17:48:03</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2812,36 +2788,44 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-03-2026 18:05:04</t>
+          <t>17-03-2026 17:04:19</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:03:57</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2849,14 +2833,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26060523020730005655</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26060523260380006422</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2873,12 +2865,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349640</t>
+          <t>347679</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91805</t>
+          <t>89844</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2888,17 +2880,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARELI </t>
+          <t xml:space="preserve">OSCAR </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t xml:space="preserve">VILLARREAL </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2908,35 +2900,31 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6961173944</t>
+          <t>6961078645</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-12-2004</t>
+          <t>21-11-1975</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KARELICORRALES9@GMAIL.COM</t>
+          <t>SAN.OSCARBB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-03-2026 18:59:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>02-03-2026 16:32:28</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2944,28 +2932,28 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-03-2026 19:05:01</t>
+          <t>18-03-2026 18:33:54</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>17-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2976,36 +2964,40 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26060523025670005681</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26060523303660006581</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>349751</t>
+          <t>349990</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>91916</t>
+          <t>92155</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3007,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIBEL </t>
+          <t xml:space="preserve">SARAHI </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,7 +3027,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6672345777</t>
+          <t>6671853221</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3046,24 +3038,20 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25-03-1967</t>
+          <t>10-04-1999</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MARIBEL_67@GMAIL.COM</t>
+          <t>SARAHIMEZVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10-03-2026 06:53:41</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-03-2026 19:25:07</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3071,17 +3059,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10-03-2026 06:55:24</t>
+          <t>10-03-2026 19:33:17</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3103,14 +3091,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26060523042870005733</t>
+          <t>26060523068710005843</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3127,12 +3115,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348670</t>
+          <t>348614</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>90779</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3142,17 +3130,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA CRISTINA </t>
+          <t xml:space="preserve">SALVADOR </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OBESO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3162,31 +3150,35 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6671262646</t>
+          <t>6671260174</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23-05-1977</t>
+          <t>23-03-1965</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>KEYCHA7@YHOTMAIL.COM</t>
+          <t>SALVADORBAJO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-03-2026 11:53:30</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>05-03-2026 06:05:05</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3194,22 +3186,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-03-2026 11:55:38</t>
+          <t>07-03-2026 07:21:41</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3226,36 +3218,44 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26060522914020005327</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26060522969080005509</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Gilberto Ramos Quintero</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349576</t>
+          <t>348670</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>90835</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3265,17 +3265,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t xml:space="preserve">ANA CRISTINA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRAGAN </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>OBESO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3285,79 +3285,63 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6672221440</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ALCAPARRA</t>
-        </is>
-      </c>
+          <t>6671262646</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22-11-1994</t>
+          <t>23-05-1977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>GIL.ALBERSO@HOTMAIL.COM</t>
+          <t>KEYCHA7@YHOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-03-2026 17:57:46</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>05-03-2026 11:53:30</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 18:01:05</t>
+          <t>05-03-2026 11:55:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:00:11</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3365,14 +3349,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26060523020360005653</t>
+          <t>26060522914020005327</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3389,12 +3373,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349625</t>
+          <t>349774</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91790</t>
+          <t>91939</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3404,17 +3388,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RAMON ESAU</t>
+          <t xml:space="preserve">ROSA ALEJANDRA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIO </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3424,35 +3408,31 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6676937404</t>
+          <t>6671016755</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20-08-1993</t>
+          <t>07-09-1990</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ESAURUBIO5831@GMAIL.COM</t>
+          <t>GUTIERREZRAGS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-03-2026 18:47:46</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>10-03-2026 08:45:11</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3460,22 +3440,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 18:50:49</t>
+          <t>10-03-2026 08:47:28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>09-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3492,36 +3472,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26060523024360005676</t>
+          <t>26060523045860005747</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>349774</t>
+          <t>349991</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>91939</t>
+          <t>92156</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3531,17 +3511,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ALEJANDRA </t>
+          <t xml:space="preserve">ALAN </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3551,63 +3531,75 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6671016755</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6676925232</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DORADO</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07-09-1990</t>
+          <t>15-09-2002</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>GUTIERREZRAGS@GMAIL.COM</t>
+          <t>ALANMEZAVZLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-03-2026 08:45:11</t>
+          <t>10-03-2026 19:27:13</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-03-2026 08:47:28</t>
+          <t>10-03-2026 19:33:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:32:45</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3615,14 +3607,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26060523045860005747</t>
+          <t>26060523068710005843</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3639,12 +3631,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>350100</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>92156</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3654,17 +3646,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALAN </t>
+          <t xml:space="preserve">DENIS ADRIANA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">ESQUIVEL </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3674,35 +3666,39 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6676925232</t>
+          <t>6673096295</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DORADO</t>
+          <t>ALGARROBO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15-09-2002</t>
+          <t>09-03-1996</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ALANMEZAVZLA@GMAIL.COM</t>
+          <t>DENISPAYAN0903@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-03-2026 19:27:13</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>11-03-2026 13:21:16</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3710,27 +3706,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-03-2026 19:33:17</t>
+          <t>12-03-2026 14:28:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-03-2026 19:32:45</t>
+          <t>12-03-2026 14:27:41</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3740,7 +3736,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3750,36 +3746,44 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26060523068710005843</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26060523123440006033</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Quintero Dominguez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>349990</t>
+          <t>350877</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>92155</t>
+          <t>93041</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3789,17 +3793,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI </t>
+          <t>ARIANNA GUADALUPE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3809,7 +3813,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6671853221</t>
+          <t>6674503791</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3820,20 +3824,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>10-04-1999</t>
+          <t>06-06-2008</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>SARAHIMEZVA@GMAIL.COM</t>
+          <t>GASTELUMSOTOARIANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10-03-2026 19:25:07</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>15-03-2026 11:28:27</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3841,22 +3849,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10-03-2026 19:33:17</t>
+          <t>17-03-2026 20:42:30</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3873,14 +3881,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26060523068710005843</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26060523274250006479</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3897,12 +3913,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>350064</t>
+          <t>349589</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>91754</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3912,17 +3928,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ALONSO </t>
+          <t xml:space="preserve">PATRICIA </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MURO </t>
+          <t>OVIEDO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>NORIS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3932,33 +3948,33 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6231180361</t>
+          <t>6674109315</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>10-09-2011</t>
+          <t>11-09-1983</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>LMURO985@GMAIL.COM</t>
+          <t>PATTYOV11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11-03-2026 09:45:44</t>
+          <t>09-03-2026 18:03:55</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3968,22 +3984,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>12-03-2026 12:18:56</t>
+          <t>09-03-2026 18:05:04</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -4000,14 +4016,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26060523121110006024</t>
+          <t>26060523020730005655</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4024,12 +4040,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>350100</t>
+          <t>350064</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>92265</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4039,17 +4055,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DENIS ADRIANA </t>
+          <t xml:space="preserve">LUIS ALONSO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t xml:space="preserve">MURO </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESQUIVEL </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4059,47 +4075,43 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6673096295</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>ALGARROBO</t>
-        </is>
-      </c>
+          <t>6231180361</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-03-1996</t>
+          <t>10-09-2011</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>DENISPAYAN0903@GMAIL.COM</t>
+          <t>LMURO985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11-03-2026 13:21:16</t>
+          <t>11-03-2026 09:45:44</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4109,7 +4121,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>12-03-2026 14:28:20</t>
+          <t>12-03-2026 12:18:56</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4117,21 +4129,13 @@
           <t>11-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>12-03-2026 14:27:41</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4139,19 +4143,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26060523123440006033</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060523121110006024</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>549</t>
@@ -4159,24 +4155,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Israel  Quintero Dominguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>350877</t>
+          <t>351405</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93041</t>
+          <t>93569</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4186,17 +4182,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ARIANNA GUADALUPE</t>
+          <t xml:space="preserve">SOCORRO ISABEL </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t>VARELAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4206,10 +4202,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6674503791</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>5530312690</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C NORTE</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4217,56 +4217,60 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-06-2008</t>
+          <t>27-06-1970</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>GASTELUMSOTOARIANA@GMAIL.COM</t>
+          <t>SOCORROISABEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15-03-2026 11:28:27</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>17-03-2026 06:30:16</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17-03-2026 20:42:30</t>
+          <t>17-03-2026 06:47:36</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>17-03-2026 06:46:44</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26060523274250006479</t>
+          <t>26060523244000006351</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4284,12 +4288,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4306,12 +4310,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>350026</t>
+          <t>351444</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>93608</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4321,17 +4325,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEORGINA LIZETTE </t>
+          <t xml:space="preserve">MARIA JOSE </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4341,14 +4345,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6671370524</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>C ORDUNA</t>
-        </is>
-      </c>
+          <t>6673511019</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4356,64 +4356,52 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14-07-1981</t>
+          <t>11-06-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>GEORGY147@HOTMAIL.COM</t>
+          <t>MJLOPEZZAVALA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11-03-2026 05:11:21</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>17-03-2026 09:45:54</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-03-2026 07:02:06</t>
+          <t>17-03-2026 09:56:41</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>16-03-2026 07:01:18</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4421,32 +4409,24 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26060523202360006243</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060523248920006377</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Brayan Ramiro Armienta Perez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4580,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>351445</t>
+          <t>351540</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93609</t>
+          <t>93704</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,17 +4595,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEODORO ALONSO </t>
+          <t>OSMAR ALEXANDER</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FRAILE</t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4635,75 +4615,63 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6673505959</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>DIEGO DE GUZMAN</t>
-        </is>
-      </c>
+          <t>6671063417</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-08-2000</t>
+          <t>12-03-2012</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TEO_ALONSO12@HOTMAIL.COM</t>
+          <t>OSMARTIRADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17-03-2026 09:50:21</t>
+          <t>17-03-2026 15:29:05</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>17-03-2026 09:56:41</t>
+          <t>19-03-2026 15:34:57</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>17-03-2026 09:55:40</t>
-        </is>
-      </c>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4711,36 +4679,44 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26060523248920006377</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26060523330960006674</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Quintero Dominguez</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351718</t>
+          <t>351717</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93882</t>
+          <t>93881</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4750,17 +4726,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ROSA ILIANA</t>
+          <t>LUIS MANUEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t>ENCINES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4770,28 +4746,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6674737628</t>
+          <t>6679968685</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-05-1977</t>
+          <t>22-07-2008</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ILIANASOTOMOLIMA@GMAIL.COM</t>
+          <t>LUISMENORT20@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>17-03-2026 20:38:02</t>
+          <t>17-03-2026 20:30:18</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4816,7 +4792,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>17-03-2026 20:47:52</t>
+          <t>17-03-2026 20:49:28</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4838,7 +4814,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26060523274460006480</t>
+          <t>26060523274500006482</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4870,12 +4846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>351405</t>
+          <t>351445</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>93609</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4885,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCORRO ISABEL </t>
+          <t xml:space="preserve">TEODORO ALONSO </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t>FRAILE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VARELAS</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4905,63 +4881,63 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5530312690</t>
+          <t>6673505959</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C NORTE</t>
+          <t>DIEGO DE GUZMAN</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>27-06-1970</t>
+          <t>12-08-2000</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SOCORROISABEL@GMAIL.COM</t>
+          <t>TEO_ALONSO12@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-03-2026 06:30:16</t>
+          <t>17-03-2026 09:50:21</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-03-2026 06:47:36</t>
+          <t>17-03-2026 09:56:41</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17-03-2026 06:46:44</t>
+          <t>17-03-2026 09:55:40</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4971,7 +4947,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4981,22 +4957,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26060523244000006351</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
-        </is>
-      </c>
+          <t>26060523248920006377</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5013,12 +4981,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>351444</t>
+          <t>351969</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93608</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5028,17 +4996,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA JOSE </t>
+          <t xml:space="preserve">JESUS EFREN </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">LUNA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5048,31 +5016,35 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6673511019</t>
+          <t>6672018442</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11-06-2000</t>
+          <t>08-10-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MJLOPEZZAVALA@GMAIL.COM</t>
+          <t>EFRENL_O8@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17-03-2026 09:45:54</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>18-03-2026 19:06:07</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5080,22 +5052,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17-03-2026 09:56:41</t>
+          <t>20-03-2026 17:52:09</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>19-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5112,14 +5084,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26060523248920006377</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26060523371470006794</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5136,12 +5116,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>350324</t>
+          <t>351952</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92488</t>
+          <t>94116</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFRAIN </t>
+          <t xml:space="preserve">MARIA LETICIA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t xml:space="preserve">GALLEGOS </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,43 +5151,47 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6671205525</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6674213362</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES MAGON </t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25-08-1964</t>
+          <t>16-09-1971</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>COMANDANCIA@BOMBEROSCULIACAN.ORG.MX</t>
+          <t>JONGAJEOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12-03-2026 13:10:55</t>
+          <t>18-03-2026 18:39:51</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5217,21 +5201,29 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>12-03-2026 13:12:30</t>
+          <t>19-03-2026 20:15:34</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:15:14</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5239,11 +5231,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26060523122060006029</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26060523343550006730</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>549</t>
@@ -5390,12 +5390,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>351960</t>
+          <t>351489</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>94124</t>
+          <t>93653</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELISA NICOLE </t>
+          <t xml:space="preserve">PAUL ALBERTO </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACOSTA </t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5425,28 +5425,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6677805160</t>
+          <t>6674481190</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01-08-2010</t>
+          <t>30-03-2006</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ELISANVA10@GMAIL.COM</t>
+          <t>PAULZEPEDA26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18-03-2026 18:47:19</t>
+          <t>17-03-2026 12:46:19</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5467,18 +5467,18 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>18-03-2026 18:51:51</t>
+          <t>20-03-2026 10:37:26</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
+          <t>19-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5489,11 +5489,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26060523304800006585</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26060523361380006765</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>1500</t>
@@ -5501,24 +5509,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>351540</t>
+          <t>348752</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93704</t>
+          <t>90917</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5528,17 +5536,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OSMAR ALEXANDER</t>
+          <t>NATHALY DENISSE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>BRUNN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5548,10 +5556,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6671063417</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6671897221</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5559,52 +5571,64 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>12-03-2012</t>
+          <t>28-02-1997</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>OSMARTIRADO@GMAIL.COM</t>
+          <t>NATHALY_BRUNN@HOMTAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-03-2026 15:29:05</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>05-03-2026 16:41:25</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>19-03-2026 15:34:57</t>
+          <t>05-03-2026 16:44:31</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:43:52</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5612,27 +5636,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26060523330960006674</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060522921900005358</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Israel  Quintero Dominguez</t>
+          <t>Jesus Gilberto Ramos Quintero</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5644,12 +5660,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>351940</t>
+          <t>351718</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>94104</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5659,17 +5675,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>ROSA ILIANA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA CRUZ </t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5679,31 +5695,35 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6673408053</t>
+          <t>6674737628</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10-03-2012</t>
+          <t>21-05-1977</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>SAN.OSCARB@GMAIL.COM</t>
+          <t>ILIANASOTOMOLIMA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18-03-2026 18:28:20</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>17-03-2026 20:38:02</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5711,28 +5731,28 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>18-03-2026 18:29:39</t>
+          <t>17-03-2026 20:47:52</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5743,36 +5763,44 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26060523303240006578</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26060523274460006480</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Benjamin  Serrano Gastelum</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>351717</t>
+          <t>351940</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93881</t>
+          <t>94104</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5782,17 +5810,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LUIS MANUEL</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ENCINES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">DE LA CRUZ </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5802,7 +5830,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6679968685</t>
+          <t>6673408053</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5813,24 +5841,20 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22-07-2008</t>
+          <t>10-03-2012</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LUISMENORT20@HOTMAIL.COM</t>
+          <t>SAN.OSCARB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17-03-2026 20:30:18</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>18-03-2026 18:28:20</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5838,28 +5862,28 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-03-2026 20:49:28</t>
+          <t>18-03-2026 18:29:39</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>17-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -5870,44 +5894,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26060523274500006482</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26060523303240006578</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Benjamin  Serrano Gastelum</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>351952</t>
+          <t>350026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>94116</t>
+          <t>92191</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5917,17 +5933,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LETICIA </t>
+          <t xml:space="preserve">GEORGINA LIZETTE </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5937,12 +5953,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6674213362</t>
+          <t>6671370524</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES MAGON </t>
+          <t>C ORDUNA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5952,17 +5968,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16-09-1971</t>
+          <t>14-07-1981</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>JONGAJEOLA@GMAIL.COM</t>
+          <t>GEORGY147@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-03-2026 18:39:51</t>
+          <t>11-03-2026 05:11:21</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5987,17 +6003,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>19-03-2026 20:15:34</t>
+          <t>16-03-2026 07:02:06</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19-03-2026 20:15:14</t>
+          <t>16-03-2026 07:01:18</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6017,7 +6033,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26060523343550006730</t>
+          <t>26060523202360006243</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -6027,20 +6043,1691 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Brayan Ramiro Armienta Perez</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>353286</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>95450</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6673291077</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>25-07-1963</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CARMEN70@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:12:48</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>27-03-2026 09:11:51</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>26-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26060523559930007387</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>ANA PAOLA GUERRA CAJERO SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>352856</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>95020</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CINTHYA NAYELI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6672015006</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>03-10-1998</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CINTHIA_NAYELI18@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:28:56</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:31:22</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26060523435780006969</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>352859</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>95023</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISMAEL </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FELIX </t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6671541558</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>04-05-1985</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ISMAEL.CAS.134@HMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:29:57</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:31:34</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26060523435790006970</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>350324</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>92488</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EFRAIN </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ARAUJO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZAZUETA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6671205525</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>25-08-1964</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>COMANDANCIA@BOMBEROSCULIACAN.ORG.MX</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:10:55</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:12:30</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26060523122060006029</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>353521</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>95685</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DANIEL OSWALDO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6678979743</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>23-12-1992</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DANIELOPEREZRUBIO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>26-03-2026 10:33:27</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:08:25</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26060523621130007522</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LETICIA ROMERO PARRA </t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>349625</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>91790</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RAMON ESAU</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUBIO </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6676937404</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>20-08-1993</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ESAURUBIO5831@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:47:46</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:50:49</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26060523024360005676</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>353543</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>95707</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GALICIA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6675473430</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>08-11-2001</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>EDUARDOGALICIAM6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>26-03-2026 12:57:58</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:01:41</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26060523533070007306</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>354003</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>96167</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUIJANO </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6672316577</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUEDUCTO </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>05-12-1980</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FERNYAD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>29-03-2026 11:00:42</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>29-03-2026 11:05:54</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>28-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>29-03-2026 11:05:17</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26060523603980007479</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>354236</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>96400</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ANAKAREN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LIZARRAGA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6671395479</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PABLO MACIAS VALENZUELA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>11-08-1990</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BATCANDYS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>30-03-2026 15:04:44</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>30-03-2026 15:10:20</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>30-03-2026 15:09:34</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26060523631350007559</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Israel  Quintero Dominguez</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352004</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94168</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IRIS MICHEL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SICAIROS </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FAVELA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6671324769</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>06-12-2011</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>MICHELSICAIROS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:32:22</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>27-03-2026 05:34:31</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>26-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26060523551520007374</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>351960</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>94124</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELISA NICOLE </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELAZQUEZ </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACOSTA </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6677805160</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>01-08-2010</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ELISANVA10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:47:19</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:51:51</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26060523304800006585</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>352833</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>94997</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAMARIS </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ELENES</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AGUIRRE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6673589767</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>05-01-1998</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ESTABATA25822@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:53:48</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:00:19</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>24-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26060523510220007238</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
           <t>LIZBETH  SALDIVAR MONTES</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Benjamin  Serrano Gastelum</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>353362</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>95526</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAFAEL </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JACOBO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6671432756</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>29-04-1982</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>RAFAELGOKOU@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>25-03-2026 15:58:20</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:03:45</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>24-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26060523505010007222</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
